--- a/AAII_Financials/Yearly/NPB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NPB_YR_FIN.xlsx
@@ -2175,7 +2175,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>420000</v>
+        <v>437000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5293300</v>
+        <v>5310300</v>
       </c>
       <c r="E60" s="3">
         <v>3425600</v>
@@ -2274,7 +2274,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1117400</v>
+        <v>1100400</v>
       </c>
       <c r="E61" s="3">
         <v>1304200</v>
